--- a/results/analysis/stage0_vs_stage3/english_native_baseline.xlsx
+++ b/results/analysis/stage0_vs_stage3/english_native_baseline.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:L91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,40 +436,55 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>original_country</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>language</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>is_english</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>cultural_region</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>is_islamic</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>real_PC1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>real_PC2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>llm_PC1</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>llm_PC2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>distance</t>
         </is>
@@ -483,31 +498,44 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>en-native</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>anthropic/claude-3.7-sonnet</t>
-        </is>
-      </c>
-      <c r="D2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E2" t="n">
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>claude-3-7-sonnet-20250219</t>
+        </is>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
         <v>3.3721445203</v>
       </c>
-      <c r="F2" t="n">
+      <c r="I2" t="n">
         <v>0.7189674986</v>
       </c>
-      <c r="G2" t="n">
-        <v>6.117175818324504</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2.459395098868036</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3.250274612845636</v>
+      <c r="J2" t="n">
+        <v>4.300565379649385</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.499666583617535</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.93159558832599</v>
       </c>
     </row>
     <row r="3">
@@ -518,31 +546,44 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>en-native</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>anthropic/claude-sonnet-4.5</t>
-        </is>
-      </c>
-      <c r="D3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4.5</t>
+        </is>
+      </c>
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
         <v>3.3721445203</v>
       </c>
-      <c r="F3" t="n">
+      <c r="I3" t="n">
         <v>0.7189674986</v>
       </c>
-      <c r="G3" t="n">
-        <v>6.497609535613809</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2.737356765276816</v>
-      </c>
-      <c r="I3" t="n">
-        <v>3.720541196356617</v>
+      <c r="J3" t="n">
+        <v>6.520779059559366</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.655830054103604</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3.696665527300108</v>
       </c>
     </row>
     <row r="4">
@@ -553,31 +594,44 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>en-native</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>deepseek/deepseek-chat-v3-0324</t>
-        </is>
-      </c>
-      <c r="D4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>deepseek-chat</t>
+        </is>
+      </c>
+      <c r="E4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
         <v>3.3721445203</v>
       </c>
-      <c r="F4" t="n">
+      <c r="I4" t="n">
         <v>0.7189674986</v>
       </c>
-      <c r="G4" t="n">
-        <v>6.548121408165519</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.243169169285635</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3.218946502165819</v>
+      <c r="J4" t="n">
+        <v>8.286787621282848</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.158396168040508</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4.934249118717513</v>
       </c>
     </row>
     <row r="5">
@@ -588,31 +642,44 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>en-native</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>google/gemini-2.0-flash-001</t>
-        </is>
-      </c>
-      <c r="D5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>deepseek-chat-v3.1</t>
+        </is>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
         <v>3.3721445203</v>
       </c>
-      <c r="F5" t="n">
+      <c r="I5" t="n">
         <v>0.7189674986</v>
       </c>
-      <c r="G5" t="n">
-        <v>5.171921397568573</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2.304226388393427</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.398383321243647</v>
+      <c r="J5" t="n">
+        <v>6.205994244144114</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.136762443368075</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.864481955468584</v>
       </c>
     </row>
     <row r="6">
@@ -623,31 +690,44 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>en-native</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>google/gemini-2.5-flash</t>
-        </is>
-      </c>
-      <c r="D6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>gemini-2.5-flash</t>
+        </is>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
         <v>3.3721445203</v>
       </c>
-      <c r="F6" t="n">
+      <c r="I6" t="n">
         <v>0.7189674986</v>
       </c>
-      <c r="G6" t="n">
-        <v>4.148647238225169</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2.74161058824746</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.166573686502214</v>
+      <c r="J6" t="n">
+        <v>6.131458290323367</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.200528252063027</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3.711058643375035</v>
       </c>
     </row>
     <row r="7">
@@ -658,31 +738,44 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>en-native</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>meta-llama/llama-3.3-70b-instruct</t>
-        </is>
-      </c>
-      <c r="D7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>gemini-2.5-pro</t>
+        </is>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
         <v>3.3721445203</v>
       </c>
-      <c r="F7" t="n">
+      <c r="I7" t="n">
         <v>0.7189674986</v>
       </c>
-      <c r="G7" t="n">
-        <v>4.543222288712538</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2.440199184372619</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2.081840929508723</v>
+      <c r="J7" t="n">
+        <v>6.111383413970556</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.968679941921401</v>
+      </c>
+      <c r="L7" t="n">
+        <v>4.250183605548758</v>
       </c>
     </row>
     <row r="8">
@@ -693,31 +786,44 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>en-native</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mistralai/mistral-nemo</t>
-        </is>
-      </c>
-      <c r="D8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" t="n">
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>gemini-3-pro-preview</t>
+        </is>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
         <v>3.3721445203</v>
       </c>
-      <c r="F8" t="n">
+      <c r="I8" t="n">
         <v>0.7189674986</v>
       </c>
-      <c r="G8" t="n">
-        <v>8.011800292115133</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.03363381555326465</v>
-      </c>
-      <c r="I8" t="n">
-        <v>4.689998714078276</v>
+      <c r="J8" t="n">
+        <v>5.869589420439573</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.871060182162022</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4.021556827274531</v>
       </c>
     </row>
     <row r="9">
@@ -728,31 +834,44 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>en-native</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>openai/gpt-4o-mini</t>
-        </is>
-      </c>
-      <c r="D9" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" t="n">
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>gemma-3-4b-it</t>
+        </is>
+      </c>
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>3.3721445203</v>
       </c>
-      <c r="F9" t="n">
+      <c r="I9" t="n">
         <v>0.7189674986</v>
       </c>
-      <c r="G9" t="n">
-        <v>6.25156348240662</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.128341309298359</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.908374198108775</v>
+      <c r="J9" t="n">
+        <v>0.1005465709483032</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.685618950434553</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.817207235035214</v>
       </c>
     </row>
     <row r="10">
@@ -763,31 +882,44 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>en-native</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>qwen/qwq-32b</t>
-        </is>
-      </c>
-      <c r="D10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" t="n">
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>gpt-4o</t>
+        </is>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
         <v>3.3721445203</v>
       </c>
-      <c r="F10" t="n">
+      <c r="I10" t="n">
         <v>0.7189674986</v>
       </c>
-      <c r="G10" t="n">
-        <v>7.475118090237792</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2.74250792078624</v>
-      </c>
-      <c r="I10" t="n">
-        <v>4.574834199818583</v>
+      <c r="J10" t="n">
+        <v>6.262349576706793</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.332204824589809</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3.309957694298546</v>
       </c>
     </row>
     <row r="11">
@@ -798,311 +930,428 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>en-native</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>x-ai/grok-code-fast-1</t>
-        </is>
-      </c>
-      <c r="D11" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" t="n">
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="E11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
         <v>3.3721445203</v>
       </c>
-      <c r="F11" t="n">
+      <c r="I11" t="n">
         <v>0.7189674986</v>
       </c>
-      <c r="G11" t="n">
-        <v>7.044172500396775</v>
-      </c>
-      <c r="H11" t="n">
-        <v>3.958733850368642</v>
-      </c>
-      <c r="I11" t="n">
-        <v>4.896925106703788</v>
+      <c r="J11" t="n">
+        <v>4.795052545747179</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.683277355525025</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3.288130194615908</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>en-native</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>anthropic/claude-3.7-sonnet</t>
-        </is>
-      </c>
-      <c r="D12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>3.146022511</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.9631136815</v>
-      </c>
-      <c r="G12" t="n">
-        <v>4.711149687186183</v>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>gpt-5.1</t>
+        </is>
+      </c>
+      <c r="E12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G12" t="b">
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.237713193943708</v>
+        <v>3.3721445203</v>
       </c>
       <c r="I12" t="n">
-        <v>1.589033659137168</v>
+        <v>0.7189674986</v>
+      </c>
+      <c r="J12" t="n">
+        <v>6.316594027548231</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.14223668111606</v>
+      </c>
+      <c r="L12" t="n">
+        <v>4.515368733193173</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>en-native</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>anthropic/claude-sonnet-4.5</t>
-        </is>
-      </c>
-      <c r="D13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" t="n">
-        <v>3.146022511</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.9631136815</v>
-      </c>
-      <c r="G13" t="n">
-        <v>6.497609535613809</v>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>grok-4.1-fast</t>
+        </is>
+      </c>
+      <c r="E13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G13" t="b">
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.737356765276816</v>
+        <v>3.3721445203</v>
       </c>
       <c r="I13" t="n">
-        <v>3.792238666525291</v>
+        <v>0.7189674986</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5.187037920688127</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.316031855752913</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.417530271922282</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>en-native</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>deepseek/deepseek-chat-v3-0324</t>
-        </is>
-      </c>
-      <c r="D14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" t="n">
-        <v>3.146022511</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.9631136815</v>
-      </c>
-      <c r="G14" t="n">
-        <v>6.548121408165519</v>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>kimi-k2</t>
+        </is>
+      </c>
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G14" t="b">
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.243169169285635</v>
+        <v>3.3721445203</v>
       </c>
       <c r="I14" t="n">
-        <v>3.413606301601532</v>
+        <v>0.7189674986</v>
+      </c>
+      <c r="J14" t="n">
+        <v>7.272959119817846</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.498063948534218</v>
+      </c>
+      <c r="L14" t="n">
+        <v>4.287369673585439</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>en-native</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>google/gemini-2.0-flash-001</t>
-        </is>
-      </c>
-      <c r="D15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" t="n">
-        <v>3.146022511</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.9631136815</v>
-      </c>
-      <c r="G15" t="n">
-        <v>5.382331099648289</v>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>llama-3.3-70b-instruct</t>
+        </is>
+      </c>
+      <c r="E15" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G15" t="b">
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.471219211030901</v>
+        <v>3.3721445203</v>
       </c>
       <c r="I15" t="n">
-        <v>2.697305765363613</v>
+        <v>0.7189674986</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.544720631222746</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.452105012282701</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.092534438722805</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>en-native</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>google/gemini-2.5-flash</t>
-        </is>
-      </c>
-      <c r="D16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" t="n">
-        <v>3.146022511</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.9631136815</v>
-      </c>
-      <c r="G16" t="n">
-        <v>5.488155306443056</v>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>mistral-medium-3.1</t>
+        </is>
+      </c>
+      <c r="E16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G16" t="b">
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.540996683102327</v>
+        <v>3.3721445203</v>
       </c>
       <c r="I16" t="n">
-        <v>2.824057506184226</v>
+        <v>0.7189674986</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5.743091160324883</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.666747661447205</v>
+      </c>
+      <c r="L16" t="n">
+        <v>3.782961255196883</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>en-native</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>meta-llama/llama-3.3-70b-instruct</t>
-        </is>
-      </c>
-      <c r="D17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" t="n">
-        <v>3.146022511</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.9631136815</v>
-      </c>
-      <c r="G17" t="n">
-        <v>6.254919812257781</v>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>mistral-nemo</t>
+        </is>
+      </c>
+      <c r="E17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G17" t="b">
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.929186110854228</v>
+        <v>3.3721445203</v>
       </c>
       <c r="I17" t="n">
-        <v>3.255539643212212</v>
+        <v>0.7189674986</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.877075035924758</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.466181235192332</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.9018221519575564</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>en-native</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>mistralai/mistral-nemo</t>
-        </is>
-      </c>
-      <c r="D18" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" t="n">
-        <v>3.146022511</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.9631136815</v>
-      </c>
-      <c r="G18" t="n">
-        <v>7.604780801440572</v>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>phi-3-mini-128k-instruct</t>
+        </is>
+      </c>
+      <c r="E18" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G18" t="b">
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5041523559158725</v>
+        <v>3.3721445203</v>
       </c>
       <c r="I18" t="n">
-        <v>4.482317591487072</v>
+        <v>0.7189674986</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.193022681341992</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.019118811544002</v>
+      </c>
+      <c r="L18" t="n">
+        <v>3.305008823213294</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>en-native</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>openai/gpt-4o-mini</t>
-        </is>
-      </c>
-      <c r="D19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" t="n">
-        <v>3.146022511</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.9631136815</v>
-      </c>
-      <c r="G19" t="n">
-        <v>5.067657305309034</v>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>qwen3-max</t>
+        </is>
+      </c>
+      <c r="E19" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G19" t="b">
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.26138224957228</v>
+        <v>3.3721445203</v>
       </c>
       <c r="I19" t="n">
-        <v>2.319090674713598</v>
+        <v>0.7189674986</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4.713538581576503</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.818114770927921</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.491135744705539</v>
       </c>
     </row>
     <row r="20">
@@ -1113,31 +1362,44 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>en-native</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>qwen/qwq-32b</t>
-        </is>
-      </c>
-      <c r="D20" t="b">
-        <v>1</v>
-      </c>
-      <c r="E20" t="n">
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>claude-3-7-sonnet-20250219</t>
+        </is>
+      </c>
+      <c r="E20" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G20" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
         <v>3.146022511</v>
       </c>
-      <c r="F20" t="n">
+      <c r="I20" t="n">
         <v>0.9631136815</v>
       </c>
-      <c r="G20" t="n">
-        <v>6.902479755151226</v>
-      </c>
-      <c r="H20" t="n">
-        <v>3.783162576670703</v>
-      </c>
-      <c r="I20" t="n">
-        <v>4.697195631255923</v>
+      <c r="J20" t="n">
+        <v>4.194141995887506</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.527202373044344</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.882797888679969</v>
       </c>
     </row>
     <row r="21">
@@ -1148,381 +1410,3404 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>en-native</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>x-ai/grok-code-fast-1</t>
-        </is>
-      </c>
-      <c r="D21" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" t="n">
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4.5</t>
+        </is>
+      </c>
+      <c r="E21" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G21" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
         <v>3.146022511</v>
       </c>
-      <c r="F21" t="n">
+      <c r="I21" t="n">
         <v>0.9631136815</v>
       </c>
-      <c r="G21" t="n">
-        <v>7.004251532249226</v>
-      </c>
-      <c r="H21" t="n">
-        <v>3.629586542541802</v>
-      </c>
-      <c r="I21" t="n">
-        <v>4.689990266416575</v>
+      <c r="J21" t="n">
+        <v>6.520779059559366</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.655830054103604</v>
+      </c>
+      <c r="L21" t="n">
+        <v>3.775482814174185</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>en-native</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>anthropic/claude-3.7-sonnet</t>
-        </is>
-      </c>
-      <c r="D22" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" t="n">
-        <v>3.4231011101</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.805576675</v>
-      </c>
-      <c r="G22" t="n">
-        <v>4.929900367671626</v>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>deepseek-chat</t>
+        </is>
+      </c>
+      <c r="E22" t="b">
+        <v>1</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G22" t="b">
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.39599354421094</v>
+        <v>3.146022511</v>
       </c>
       <c r="I22" t="n">
-        <v>2.190860520546466</v>
+        <v>0.9631136815</v>
+      </c>
+      <c r="J22" t="n">
+        <v>6.328914947920498</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.7097768889547091</v>
+      </c>
+      <c r="L22" t="n">
+        <v>3.192958470676191</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>en-native</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>anthropic/claude-sonnet-4.5</t>
-        </is>
-      </c>
-      <c r="D23" t="b">
-        <v>1</v>
-      </c>
-      <c r="E23" t="n">
-        <v>3.4231011101</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.805576675</v>
-      </c>
-      <c r="G23" t="n">
-        <v>4.543235232416667</v>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>deepseek-chat-v3.1</t>
+        </is>
+      </c>
+      <c r="E23" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G23" t="b">
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.835796877747768</v>
+        <v>3.146022511</v>
       </c>
       <c r="I23" t="n">
-        <v>2.318726918725731</v>
+        <v>0.9631136815</v>
+      </c>
+      <c r="J23" t="n">
+        <v>7.272959119817846</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.498063948534218</v>
+      </c>
+      <c r="L23" t="n">
+        <v>4.403144114774052</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>en-native</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>deepseek/deepseek-chat-v3-0324</t>
-        </is>
-      </c>
-      <c r="D24" t="b">
-        <v>1</v>
-      </c>
-      <c r="E24" t="n">
-        <v>3.4231011101</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.805576675</v>
-      </c>
-      <c r="G24" t="n">
-        <v>6.875844476760944</v>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>gemini-2.5-flash</t>
+        </is>
+      </c>
+      <c r="E24" t="b">
+        <v>1</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G24" t="b">
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.08433413934914055</v>
+        <v>3.146022511</v>
       </c>
       <c r="I24" t="n">
-        <v>3.565582422763033</v>
+        <v>0.9631136815</v>
+      </c>
+      <c r="J24" t="n">
+        <v>6.852184585589165</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.711065284731558</v>
+      </c>
+      <c r="L24" t="n">
+        <v>4.097678871063817</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>en-native</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>google/gemini-2.0-flash-001</t>
-        </is>
-      </c>
-      <c r="D25" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" t="n">
-        <v>3.4231011101</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.805576675</v>
-      </c>
-      <c r="G25" t="n">
-        <v>5.171921397568573</v>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>gemini-2.5-pro</t>
+        </is>
+      </c>
+      <c r="E25" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G25" t="b">
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2.304226388393427</v>
+        <v>3.146022511</v>
       </c>
       <c r="I25" t="n">
-        <v>2.303111669310861</v>
+        <v>0.9631136815</v>
+      </c>
+      <c r="J25" t="n">
+        <v>6.947708790315211</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.695158242916017</v>
+      </c>
+      <c r="L25" t="n">
+        <v>4.681547399300404</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>en-native</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>google/gemini-2.5-flash</t>
-        </is>
-      </c>
-      <c r="D26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" t="n">
-        <v>3.4231011101</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.805576675</v>
-      </c>
-      <c r="G26" t="n">
-        <v>6.190108945900008</v>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>gemini-3-pro-preview</t>
+        </is>
+      </c>
+      <c r="E26" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G26" t="b">
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.672741284640731</v>
+        <v>3.146022511</v>
       </c>
       <c r="I26" t="n">
-        <v>2.899708058338288</v>
+        <v>0.9631136815</v>
+      </c>
+      <c r="J26" t="n">
+        <v>5.046832767680632</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.315422990732264</v>
+      </c>
+      <c r="L26" t="n">
+        <v>2.332770905969666</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>en-native</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>meta-llama/llama-3.3-70b-instruct</t>
-        </is>
-      </c>
-      <c r="D27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E27" t="n">
-        <v>3.4231011101</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.805576675</v>
-      </c>
-      <c r="G27" t="n">
-        <v>4.543222288712538</v>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>gemma-3-4b-it</t>
+        </is>
+      </c>
+      <c r="E27" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G27" t="b">
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>2.440199184372619</v>
+        <v>3.146022511</v>
       </c>
       <c r="I27" t="n">
-        <v>1.981580733385339</v>
+        <v>0.9631136815</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.448332997134</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.734686189286775</v>
+      </c>
+      <c r="L27" t="n">
+        <v>2.453694935365133</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>en-native</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>mistralai/mistral-nemo</t>
-        </is>
-      </c>
-      <c r="D28" t="b">
-        <v>1</v>
-      </c>
-      <c r="E28" t="n">
-        <v>3.4231011101</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.805576675</v>
-      </c>
-      <c r="G28" t="n">
-        <v>8.399741560759436</v>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>gpt-4o</t>
+        </is>
+      </c>
+      <c r="E28" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G28" t="b">
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.09321413209537002</v>
+        <v>3.146022511</v>
       </c>
       <c r="I28" t="n">
-        <v>5.057150886621725</v>
+        <v>0.9631136815</v>
+      </c>
+      <c r="J28" t="n">
+        <v>6.385742878451225</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.317964949905841</v>
+      </c>
+      <c r="L28" t="n">
+        <v>3.259096114257377</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>en-native</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>openai/gpt-4o-mini</t>
-        </is>
-      </c>
-      <c r="D29" t="b">
-        <v>1</v>
-      </c>
-      <c r="E29" t="n">
-        <v>3.4231011101</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.805576675</v>
-      </c>
-      <c r="G29" t="n">
-        <v>6.25156348240662</v>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="E29" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G29" t="b">
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.128341309298359</v>
+        <v>3.146022511</v>
       </c>
       <c r="I29" t="n">
-        <v>2.846818645560013</v>
+        <v>0.9631136815</v>
+      </c>
+      <c r="J29" t="n">
+        <v>5.219090105065609</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.687275589764694</v>
+      </c>
+      <c r="L29" t="n">
+        <v>2.195909770219746</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>en-native</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>qwen/qwq-32b</t>
-        </is>
-      </c>
-      <c r="D30" t="b">
-        <v>1</v>
-      </c>
-      <c r="E30" t="n">
-        <v>3.4231011101</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.805576675</v>
-      </c>
-      <c r="G30" t="n">
-        <v>6.484114076376939</v>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>gpt-5.1</t>
+        </is>
+      </c>
+      <c r="E30" t="b">
+        <v>1</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G30" t="b">
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>3.091125845203146</v>
+        <v>3.146022511</v>
       </c>
       <c r="I30" t="n">
-        <v>3.820148608252281</v>
+        <v>0.9631136815</v>
+      </c>
+      <c r="J30" t="n">
+        <v>7.136111094471387</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.617383413816423</v>
+      </c>
+      <c r="L30" t="n">
+        <v>4.319423022951902</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>grok-4.1-fast</t>
+        </is>
+      </c>
+      <c r="E31" t="b">
+        <v>1</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G31" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3.146022511</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.9631136815</v>
+      </c>
+      <c r="J31" t="n">
+        <v>6.544596670605965</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.216155233913962</v>
+      </c>
+      <c r="L31" t="n">
+        <v>3.407981271308494</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>kimi-k2</t>
+        </is>
+      </c>
+      <c r="E32" t="b">
+        <v>1</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G32" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3.146022511</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.9631136815</v>
+      </c>
+      <c r="J32" t="n">
+        <v>7.085106229465735</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.887842016019568</v>
+      </c>
+      <c r="L32" t="n">
+        <v>4.906161062564442</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>llama-3.3-70b-instruct</t>
+        </is>
+      </c>
+      <c r="E33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3.146022511</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.9631136815</v>
+      </c>
+      <c r="J33" t="n">
+        <v>4.544720631222746</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.452105012282701</v>
+      </c>
+      <c r="L33" t="n">
+        <v>2.042902742340095</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>mistral-medium-3.1</t>
+        </is>
+      </c>
+      <c r="E34" t="b">
+        <v>1</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3.146022511</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.9631136815</v>
+      </c>
+      <c r="J34" t="n">
+        <v>5.616592900210193</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.462435140732388</v>
+      </c>
+      <c r="L34" t="n">
+        <v>3.514303032554495</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>mistral-nemo</t>
+        </is>
+      </c>
+      <c r="E35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G35" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>3.146022511</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.9631136815</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.705774218956426</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.381316932440867</v>
+      </c>
+      <c r="L35" t="n">
+        <v>2.457951488843558</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>phi-3-mini-128k-instruct</t>
+        </is>
+      </c>
+      <c r="E36" t="b">
+        <v>1</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G36" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3.146022511</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.9631136815</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.600681133474161</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.461252828253165</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.7386066798843284</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>qwen3-max</t>
+        </is>
+      </c>
+      <c r="E37" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G37" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>3.146022511</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.9631136815</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.702929038465451</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.652255646983513</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.778579618653922</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>en-native</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>x-ai/grok-code-fast-1</t>
-        </is>
-      </c>
-      <c r="D31" t="b">
-        <v>1</v>
-      </c>
-      <c r="E31" t="n">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>claude-3-7-sonnet-20250219</t>
+        </is>
+      </c>
+      <c r="E38" t="b">
+        <v>1</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G38" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
         <v>3.4231011101</v>
       </c>
-      <c r="F31" t="n">
+      <c r="I38" t="n">
         <v>0.805576675</v>
       </c>
-      <c r="G31" t="n">
-        <v>6.583311574312287</v>
-      </c>
-      <c r="H31" t="n">
-        <v>1.501620612459553</v>
-      </c>
-      <c r="I31" t="n">
-        <v>3.235955398486054</v>
+      <c r="J38" t="n">
+        <v>4.300565379649385</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.499666583617535</v>
+      </c>
+      <c r="L38" t="n">
+        <v>2.833383839166637</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4.5</t>
+        </is>
+      </c>
+      <c r="E39" t="b">
+        <v>1</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G39" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>3.4231011101</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.805576675</v>
+      </c>
+      <c r="J39" t="n">
+        <v>6.520779059559366</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.655830054103604</v>
+      </c>
+      <c r="L39" t="n">
+        <v>3.608191547777236</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>deepseek-chat</t>
+        </is>
+      </c>
+      <c r="E40" t="b">
+        <v>1</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G40" t="b">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>3.4231011101</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.805576675</v>
+      </c>
+      <c r="J40" t="n">
+        <v>5.9533010715773</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1.050771431219963</v>
+      </c>
+      <c r="L40" t="n">
+        <v>2.542052775521684</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>deepseek-chat-v3.1</t>
+        </is>
+      </c>
+      <c r="E41" t="b">
+        <v>1</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G41" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>3.4231011101</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.805576675</v>
+      </c>
+      <c r="J41" t="n">
+        <v>8.297686800318679</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1.146767420429239</v>
+      </c>
+      <c r="L41" t="n">
+        <v>4.8865117186037</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>gemini-2.5-flash</t>
+        </is>
+      </c>
+      <c r="E42" t="b">
+        <v>1</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G42" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>3.4231011101</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.805576675</v>
+      </c>
+      <c r="J42" t="n">
+        <v>6.398023534138464</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1.779994403057519</v>
+      </c>
+      <c r="L42" t="n">
+        <v>3.130439799421108</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>gemini-2.5-pro</t>
+        </is>
+      </c>
+      <c r="E43" t="b">
+        <v>1</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G43" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>3.4231011101</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.805576675</v>
+      </c>
+      <c r="J43" t="n">
+        <v>6.154980130113881</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.922164951476333</v>
+      </c>
+      <c r="L43" t="n">
+        <v>4.144428243444652</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>gemini-3-pro-preview</t>
+        </is>
+      </c>
+      <c r="E44" t="b">
+        <v>1</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G44" t="b">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>3.4231011101</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.805576675</v>
+      </c>
+      <c r="J44" t="n">
+        <v>5.541623281440994</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2.821667791921278</v>
+      </c>
+      <c r="L44" t="n">
+        <v>2.924510143971508</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>gemma-3-4b-it</t>
+        </is>
+      </c>
+      <c r="E45" t="b">
+        <v>1</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G45" t="b">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>3.4231011101</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.805576675</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.448332997134</v>
+      </c>
+      <c r="K45" t="n">
+        <v>2.734686189286775</v>
+      </c>
+      <c r="L45" t="n">
+        <v>2.760647137556529</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>gpt-4o</t>
+        </is>
+      </c>
+      <c r="E46" t="b">
+        <v>1</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G46" t="b">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>3.4231011101</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.805576675</v>
+      </c>
+      <c r="J46" t="n">
+        <v>6.563246003571567</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.2518188684175136</v>
+      </c>
+      <c r="L46" t="n">
+        <v>3.188598071307609</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="E47" t="b">
+        <v>1</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>3.4231011101</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.805576675</v>
+      </c>
+      <c r="J47" t="n">
+        <v>6.243817785566439</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.335979061659716</v>
+      </c>
+      <c r="L47" t="n">
+        <v>2.859539207933567</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>gpt-5.1</t>
+        </is>
+      </c>
+      <c r="E48" t="b">
+        <v>1</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G48" t="b">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>3.4231011101</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.805576675</v>
+      </c>
+      <c r="J48" t="n">
+        <v>6.316594027548231</v>
+      </c>
+      <c r="K48" t="n">
+        <v>4.14223668111606</v>
+      </c>
+      <c r="L48" t="n">
+        <v>4.416514605402941</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>grok-4.1-fast</t>
+        </is>
+      </c>
+      <c r="E49" t="b">
+        <v>1</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G49" t="b">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>3.4231011101</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.805576675</v>
+      </c>
+      <c r="J49" t="n">
+        <v>6.237881674085247</v>
+      </c>
+      <c r="K49" t="n">
+        <v>4.172992462636219</v>
+      </c>
+      <c r="L49" t="n">
+        <v>4.388904044315706</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>kimi-k2</t>
+        </is>
+      </c>
+      <c r="E50" t="b">
+        <v>1</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G50" t="b">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>3.4231011101</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.805576675</v>
+      </c>
+      <c r="J50" t="n">
+        <v>7.489068912431352</v>
+      </c>
+      <c r="K50" t="n">
+        <v>2.65999194011761</v>
+      </c>
+      <c r="L50" t="n">
+        <v>4.468886902249425</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>llama-3.3-70b-instruct</t>
+        </is>
+      </c>
+      <c r="E51" t="b">
+        <v>1</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G51" t="b">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>3.4231011101</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.805576675</v>
+      </c>
+      <c r="J51" t="n">
+        <v>4.544720631222746</v>
+      </c>
+      <c r="K51" t="n">
+        <v>2.452105012282701</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1.992256488416728</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>mistral-medium-3.1</t>
+        </is>
+      </c>
+      <c r="E52" t="b">
+        <v>1</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G52" t="b">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>3.4231011101</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.805576675</v>
+      </c>
+      <c r="J52" t="n">
+        <v>5.763166036677694</v>
+      </c>
+      <c r="K52" t="n">
+        <v>2.898595971588831</v>
+      </c>
+      <c r="L52" t="n">
+        <v>3.139527613589705</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>mistral-nemo</t>
+        </is>
+      </c>
+      <c r="E53" t="b">
+        <v>1</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G53" t="b">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>3.4231011101</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.805576675</v>
+      </c>
+      <c r="J53" t="n">
+        <v>3.994540706874494</v>
+      </c>
+      <c r="K53" t="n">
+        <v>3.057489091884045</v>
+      </c>
+      <c r="L53" t="n">
+        <v>2.323284904198867</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>phi-3-mini-128k-instruct</t>
+        </is>
+      </c>
+      <c r="E54" t="b">
+        <v>1</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G54" t="b">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>3.4231011101</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.805576675</v>
+      </c>
+      <c r="J54" t="n">
+        <v>2.853677653703542</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1.8698778696828</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1.207054309340605</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>qwen3-max</t>
+        </is>
+      </c>
+      <c r="E55" t="b">
+        <v>1</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>3.4231011101</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.805576675</v>
+      </c>
+      <c r="J55" t="n">
+        <v>6.183940570906376</v>
+      </c>
+      <c r="K55" t="n">
+        <v>2.685594635391491</v>
+      </c>
+      <c r="L55" t="n">
+        <v>3.340164974928667</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>claude-3-7-sonnet-20250219</t>
+        </is>
+      </c>
+      <c r="E56" t="b">
+        <v>1</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G56" t="b">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>3.1259015109</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1.1141712012</v>
+      </c>
+      <c r="J56" t="n">
+        <v>4.320640256002196</v>
+      </c>
+      <c r="K56" t="n">
+        <v>2.731514893759161</v>
+      </c>
+      <c r="L56" t="n">
+        <v>2.010771316910323</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4.5</t>
+        </is>
+      </c>
+      <c r="E57" t="b">
+        <v>1</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G57" t="b">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>3.1259015109</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1.1141712012</v>
+      </c>
+      <c r="J57" t="n">
+        <v>4.920299460806858</v>
+      </c>
+      <c r="K57" t="n">
+        <v>2.520771803103271</v>
+      </c>
+      <c r="L57" t="n">
+        <v>2.279997643837506</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>deepseek-chat</t>
+        </is>
+      </c>
+      <c r="E58" t="b">
+        <v>1</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G58" t="b">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>3.1259015109</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1.1141712012</v>
+      </c>
+      <c r="J58" t="n">
+        <v>3.05609737885531</v>
+      </c>
+      <c r="K58" t="n">
+        <v>3.204511159939719</v>
+      </c>
+      <c r="L58" t="n">
+        <v>2.091505142225207</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>deepseek-chat-v3.1</t>
+        </is>
+      </c>
+      <c r="E59" t="b">
+        <v>1</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G59" t="b">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>3.1259015109</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1.1141712012</v>
+      </c>
+      <c r="J59" t="n">
+        <v>3.559760242270084</v>
+      </c>
+      <c r="K59" t="n">
+        <v>2.631598989600102</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1.578233345166323</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>gemini-2.5-flash</t>
+        </is>
+      </c>
+      <c r="E60" t="b">
+        <v>1</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G60" t="b">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>3.1259015109</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1.1141712012</v>
+      </c>
+      <c r="J60" t="n">
+        <v>3.946576645311679</v>
+      </c>
+      <c r="K60" t="n">
+        <v>2.601609729005105</v>
+      </c>
+      <c r="L60" t="n">
+        <v>1.698817544717691</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>gemini-2.5-pro</t>
+        </is>
+      </c>
+      <c r="E61" t="b">
+        <v>1</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G61" t="b">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>3.1259015109</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1.1141712012</v>
+      </c>
+      <c r="J61" t="n">
+        <v>4.752697808749028</v>
+      </c>
+      <c r="K61" t="n">
+        <v>3.931241450680446</v>
+      </c>
+      <c r="L61" t="n">
+        <v>3.253052564162333</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>gemini-3-pro-preview</t>
+        </is>
+      </c>
+      <c r="E62" t="b">
+        <v>1</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G62" t="b">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>3.1259015109</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1.1141712012</v>
+      </c>
+      <c r="J62" t="n">
+        <v>4.905042302261374</v>
+      </c>
+      <c r="K62" t="n">
+        <v>3.195375165816749</v>
+      </c>
+      <c r="L62" t="n">
+        <v>2.738019703695072</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>gemma-3-4b-it</t>
+        </is>
+      </c>
+      <c r="E63" t="b">
+        <v>1</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G63" t="b">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>3.1259015109</v>
+      </c>
+      <c r="I63" t="n">
+        <v>1.1141712012</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.1005465709483032</v>
+      </c>
+      <c r="K63" t="n">
+        <v>2.685618950434553</v>
+      </c>
+      <c r="L63" t="n">
+        <v>3.40913780027509</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>gpt-4o</t>
+        </is>
+      </c>
+      <c r="E64" t="b">
+        <v>1</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G64" t="b">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>3.1259015109</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1.1141712012</v>
+      </c>
+      <c r="J64" t="n">
+        <v>5.651452798444648</v>
+      </c>
+      <c r="K64" t="n">
+        <v>2.641603966661267</v>
+      </c>
+      <c r="L64" t="n">
+        <v>2.951518280313216</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="E65" t="b">
+        <v>1</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G65" t="b">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>3.1259015109</v>
+      </c>
+      <c r="I65" t="n">
+        <v>1.1141712012</v>
+      </c>
+      <c r="J65" t="n">
+        <v>6.731598997701705</v>
+      </c>
+      <c r="K65" t="n">
+        <v>3.533230251332625</v>
+      </c>
+      <c r="L65" t="n">
+        <v>4.34199275153203</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>gpt-5.1</t>
+        </is>
+      </c>
+      <c r="E66" t="b">
+        <v>1</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G66" t="b">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>3.1259015109</v>
+      </c>
+      <c r="I66" t="n">
+        <v>1.1141712012</v>
+      </c>
+      <c r="J66" t="n">
+        <v>4.752697808749028</v>
+      </c>
+      <c r="K66" t="n">
+        <v>3.931241450680446</v>
+      </c>
+      <c r="L66" t="n">
+        <v>3.253052564162333</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>grok-4.1-fast</t>
+        </is>
+      </c>
+      <c r="E67" t="b">
+        <v>1</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G67" t="b">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>3.1259015109</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1.1141712012</v>
+      </c>
+      <c r="J67" t="n">
+        <v>4.536588016135521</v>
+      </c>
+      <c r="K67" t="n">
+        <v>3.769313459097054</v>
+      </c>
+      <c r="L67" t="n">
+        <v>3.006628814091336</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>kimi-k2</t>
+        </is>
+      </c>
+      <c r="E68" t="b">
+        <v>1</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G68" t="b">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>3.1259015109</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1.1141712012</v>
+      </c>
+      <c r="J68" t="n">
+        <v>4.688932509647867</v>
+      </c>
+      <c r="K68" t="n">
+        <v>3.033447174233357</v>
+      </c>
+      <c r="L68" t="n">
+        <v>2.475214367223554</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>llama-3.3-70b-instruct</t>
+        </is>
+      </c>
+      <c r="E69" t="b">
+        <v>1</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G69" t="b">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>3.1259015109</v>
+      </c>
+      <c r="I69" t="n">
+        <v>1.1141712012</v>
+      </c>
+      <c r="J69" t="n">
+        <v>2.960101037465421</v>
+      </c>
+      <c r="K69" t="n">
+        <v>2.842342080255992</v>
+      </c>
+      <c r="L69" t="n">
+        <v>1.736106098200306</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>mistral-medium-3.1</t>
+        </is>
+      </c>
+      <c r="E70" t="b">
+        <v>1</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G70" t="b">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>3.1259015109</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1.1141712012</v>
+      </c>
+      <c r="J70" t="n">
+        <v>4.18837063884266</v>
+      </c>
+      <c r="K70" t="n">
+        <v>2.699229488764483</v>
+      </c>
+      <c r="L70" t="n">
+        <v>1.908206074512941</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>mistral-nemo</t>
+        </is>
+      </c>
+      <c r="E71" t="b">
+        <v>1</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G71" t="b">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>3.1259015109</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1.1141712012</v>
+      </c>
+      <c r="J71" t="n">
+        <v>3.453037476606328</v>
+      </c>
+      <c r="K71" t="n">
+        <v>3.462183000952664</v>
+      </c>
+      <c r="L71" t="n">
+        <v>2.370691323609288</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>phi-3-mini-128k-instruct</t>
+        </is>
+      </c>
+      <c r="E72" t="b">
+        <v>1</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G72" t="b">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>3.1259015109</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1.1141712012</v>
+      </c>
+      <c r="J72" t="n">
+        <v>2.600681133474161</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1.461252828253165</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.6295411826887998</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>qwen3-max</t>
+        </is>
+      </c>
+      <c r="E73" t="b">
+        <v>1</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G73" t="b">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>3.1259015109</v>
+      </c>
+      <c r="I73" t="n">
+        <v>1.1141712012</v>
+      </c>
+      <c r="J73" t="n">
+        <v>3.983463372927553</v>
+      </c>
+      <c r="K73" t="n">
+        <v>2.848306778851347</v>
+      </c>
+      <c r="L73" t="n">
+        <v>1.934590020877895</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>claude-3-7-sonnet-20250219</t>
+        </is>
+      </c>
+      <c r="E74" t="b">
+        <v>1</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G74" t="b">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>2.0833316426</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.3218169518</v>
+      </c>
+      <c r="J74" t="n">
+        <v>4.462092326999803</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1.938590022478976</v>
+      </c>
+      <c r="L74" t="n">
+        <v>2.876188025098315</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4.5</t>
+        </is>
+      </c>
+      <c r="E75" t="b">
+        <v>1</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G75" t="b">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>2.0833316426</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.3218169518</v>
+      </c>
+      <c r="J75" t="n">
+        <v>4.551703859498619</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1.896205493347551</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.927722780748414</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>deepseek-chat</t>
+        </is>
+      </c>
+      <c r="E76" t="b">
+        <v>1</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G76" t="b">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>2.0833316426</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.3218169518</v>
+      </c>
+      <c r="J76" t="n">
+        <v>4.307284617201418</v>
+      </c>
+      <c r="K76" t="n">
+        <v>1.69151063742111</v>
+      </c>
+      <c r="L76" t="n">
+        <v>2.611901151588405</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>deepseek-chat-v3.1</t>
+        </is>
+      </c>
+      <c r="E77" t="b">
+        <v>1</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G77" t="b">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>2.0833316426</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.3218169518</v>
+      </c>
+      <c r="J77" t="n">
+        <v>4.332665470456324</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1.304568376315573</v>
+      </c>
+      <c r="L77" t="n">
+        <v>2.454649268536377</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>gemini-2.5-flash</t>
+        </is>
+      </c>
+      <c r="E78" t="b">
+        <v>1</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G78" t="b">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>2.0833316426</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.3218169518</v>
+      </c>
+      <c r="J78" t="n">
+        <v>4.551703859498619</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1.896205493347551</v>
+      </c>
+      <c r="L78" t="n">
+        <v>2.927722780748414</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>gemini-2.5-pro</t>
+        </is>
+      </c>
+      <c r="E79" t="b">
+        <v>1</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G79" t="b">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>2.0833316426</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.3218169518</v>
+      </c>
+      <c r="J79" t="n">
+        <v>4.531628983145808</v>
+      </c>
+      <c r="K79" t="n">
+        <v>2.664357183205925</v>
+      </c>
+      <c r="L79" t="n">
+        <v>3.388459030810171</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>gemini-3-pro-preview</t>
+        </is>
+      </c>
+      <c r="E80" t="b">
+        <v>1</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G80" t="b">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>2.0833316426</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.3218169518</v>
+      </c>
+      <c r="J80" t="n">
+        <v>4.84598013361261</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1.478891636435393</v>
+      </c>
+      <c r="L80" t="n">
+        <v>2.995170865028963</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>gemma-3-4b-it</t>
+        </is>
+      </c>
+      <c r="E81" t="b">
+        <v>1</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G81" t="b">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>2.0833316426</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.3218169518</v>
+      </c>
+      <c r="J81" t="n">
+        <v>-0.130348243546847</v>
+      </c>
+      <c r="K81" t="n">
+        <v>2.576370443063906</v>
+      </c>
+      <c r="L81" t="n">
+        <v>3.159650310287736</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>gpt-4o</t>
+        </is>
+      </c>
+      <c r="E82" t="b">
+        <v>1</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G82" t="b">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>2.0833316426</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.3218169518</v>
+      </c>
+      <c r="J82" t="n">
+        <v>6.57040559378891</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0.4847626194325642</v>
+      </c>
+      <c r="L82" t="n">
+        <v>4.490031618378458</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="E83" t="b">
+        <v>1</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G83" t="b">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>2.0833316426</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.3218169518</v>
+      </c>
+      <c r="J83" t="n">
+        <v>5.879415409331503</v>
+      </c>
+      <c r="K83" t="n">
+        <v>2.713424422058147</v>
+      </c>
+      <c r="L83" t="n">
+        <v>4.48665111813221</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>gpt-5.1</t>
+        </is>
+      </c>
+      <c r="E84" t="b">
+        <v>1</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>2.0833316426</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.3218169518</v>
+      </c>
+      <c r="J84" t="n">
+        <v>6.112501807644422</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0.2252148680897943</v>
+      </c>
+      <c r="L84" t="n">
+        <v>4.030328048864168</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>grok-4.1-fast</t>
+        </is>
+      </c>
+      <c r="E85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G85" t="b">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>2.0833316426</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.3218169518</v>
+      </c>
+      <c r="J85" t="n">
+        <v>4.503372080884413</v>
+      </c>
+      <c r="K85" t="n">
+        <v>1.112651124137184</v>
+      </c>
+      <c r="L85" t="n">
+        <v>2.545980049228204</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>kimi-k2</t>
+        </is>
+      </c>
+      <c r="E86" t="b">
+        <v>1</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G86" t="b">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>2.0833316426</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.3218169518</v>
+      </c>
+      <c r="J86" t="n">
+        <v>6.32861160025793</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0.3871428596731868</v>
+      </c>
+      <c r="L86" t="n">
+        <v>4.245782541903385</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>llama-3.3-70b-instruct</t>
+        </is>
+      </c>
+      <c r="E87" t="b">
+        <v>1</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G87" t="b">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>2.0833316426</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.3218169518</v>
+      </c>
+      <c r="J87" t="n">
+        <v>3.859976662430193</v>
+      </c>
+      <c r="K87" t="n">
+        <v>1.097700109185549</v>
+      </c>
+      <c r="L87" t="n">
+        <v>1.938675372619664</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>mistral-medium-3.1</t>
+        </is>
+      </c>
+      <c r="E88" t="b">
+        <v>1</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G88" t="b">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>2.0833316426</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0.3218169518</v>
+      </c>
+      <c r="J88" t="n">
+        <v>4.899921236791479</v>
+      </c>
+      <c r="K88" t="n">
+        <v>2.966289463680122</v>
+      </c>
+      <c r="L88" t="n">
+        <v>3.863471471125066</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>mistral-nemo</t>
+        </is>
+      </c>
+      <c r="E89" t="b">
+        <v>1</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G89" t="b">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>2.0833316426</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0.3218169518</v>
+      </c>
+      <c r="J89" t="n">
+        <v>1.465629267798177</v>
+      </c>
+      <c r="K89" t="n">
+        <v>5.513161101077996</v>
+      </c>
+      <c r="L89" t="n">
+        <v>5.227964259640524</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>phi-3-mini-128k-instruct</t>
+        </is>
+      </c>
+      <c r="E90" t="b">
+        <v>1</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G90" t="b">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>2.0833316426</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.3218169518</v>
+      </c>
+      <c r="J90" t="n">
+        <v>2.600681133474161</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1.461252828253165</v>
+      </c>
+      <c r="L90" t="n">
+        <v>1.251385077526637</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>en-native</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>qwen3-max</t>
+        </is>
+      </c>
+      <c r="E91" t="b">
+        <v>1</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>English-Speaking</t>
+        </is>
+      </c>
+      <c r="G91" t="b">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>2.0833316426</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.3218169518</v>
+      </c>
+      <c r="J91" t="n">
+        <v>3.482001528044616</v>
+      </c>
+      <c r="K91" t="n">
+        <v>2.583875982545016</v>
+      </c>
+      <c r="L91" t="n">
+        <v>2.659546673217964</v>
       </c>
     </row>
   </sheetData>
